--- a/CNN/golden_py_model/generated/CNN_v4_포트명세_모듈별.xlsx
+++ b/CNN/golden_py_model/generated/CNN_v4_포트명세_모듈별.xlsx
@@ -3417,8 +3417,10 @@
       <x:c r="A9" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>48</x:v>
+      <x:c r="B9" s="6" t="inlineStr">
+        <x:is>
+          <x:t>out</x:t>
+        </x:is>
       </x:c>
       <x:c r="C9">
         <x:v>1</x:v>
